--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129190348</v>
       </c>
       <c r="B2" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>129190349</v>
       </c>
       <c r="B3" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129190348</v>
       </c>
       <c r="B2" t="n">
-        <v>91454</v>
+        <v>91461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>129190349</v>
       </c>
       <c r="B3" t="n">
-        <v>91454</v>
+        <v>91461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129190348</v>
       </c>
       <c r="B2" t="n">
-        <v>91461</v>
+        <v>91463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>129190349</v>
       </c>
       <c r="B3" t="n">
-        <v>91461</v>
+        <v>91463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129190348</v>
       </c>
       <c r="B2" t="n">
-        <v>91463</v>
+        <v>91466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>129190349</v>
       </c>
       <c r="B3" t="n">
-        <v>91463</v>
+        <v>91466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129190348</v>
       </c>
       <c r="B2" t="n">
-        <v>91466</v>
+        <v>91468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>129190349</v>
       </c>
       <c r="B3" t="n">
-        <v>91466</v>
+        <v>91468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129190348</v>
       </c>
       <c r="B2" t="n">
-        <v>91468</v>
+        <v>91472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>129190349</v>
       </c>
       <c r="B3" t="n">
-        <v>91468</v>
+        <v>91472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129190348</v>
       </c>
       <c r="B2" t="n">
-        <v>91472</v>
+        <v>91473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>129190349</v>
       </c>
       <c r="B3" t="n">
-        <v>91472</v>
+        <v>91473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129190348</v>
       </c>
       <c r="B2" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>129190349</v>
       </c>
       <c r="B3" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129190348</v>
       </c>
       <c r="B2" t="n">
-        <v>91476</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>129190349</v>
       </c>
       <c r="B3" t="n">
-        <v>91476</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,6 +869,107 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129994792</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92920</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Samonoajvegåbbå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>705705</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7412192</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Signe Vendike</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -874,7 +874,7 @@
         <v>129994792</v>
       </c>
       <c r="B4" t="n">
-        <v>92920</v>
+        <v>92923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -874,7 +874,7 @@
         <v>129994792</v>
       </c>
       <c r="B4" t="n">
-        <v>92923</v>
+        <v>92924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -874,7 +874,7 @@
         <v>129994792</v>
       </c>
       <c r="B4" t="n">
-        <v>92924</v>
+        <v>92941</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -874,7 +874,7 @@
         <v>129994792</v>
       </c>
       <c r="B4" t="n">
-        <v>92957</v>
+        <v>92959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -874,7 +874,7 @@
         <v>129994792</v>
       </c>
       <c r="B4" t="n">
-        <v>92959</v>
+        <v>93046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -773,48 +773,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129190349</v>
+        <v>129994792</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>93046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ládnjoajvve, Lu lm</t>
+          <t>Samonoajvegåbbå, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>705597</v>
+        <v>705705</v>
       </c>
       <c r="R3" t="n">
-        <v>7412174</v>
+        <v>7412192</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -838,12 +838,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -852,119 +852,21 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>129994792</v>
-      </c>
-      <c r="B4" t="n">
-        <v>93046</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5964</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Sarcodon imbricatus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Samonoajvegåbbå, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>705705</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7412192</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Greensway AB</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
           <t>Signe Vendike</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129190348</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -773,48 +773,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129994792</v>
+        <v>129190349</v>
       </c>
       <c r="B3" t="n">
-        <v>93046</v>
+        <v>91831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Samonoajvegåbbå, Lu lm</t>
+          <t>Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>705705</v>
+        <v>705597</v>
       </c>
       <c r="R3" t="n">
-        <v>7412192</v>
+        <v>7412174</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -838,12 +838,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -852,21 +852,119 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129994792</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Samonoajvegåbbå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>705705</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7412192</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Greensway AB</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Signe Vendike</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>

--- a/artfynd/A 32982-2023 artfynd.xlsx
+++ b/artfynd/A 32982-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129190348</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129190349</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,8 +984,18 @@
           <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129994792</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>